--- a/Dati/Resa estrattiva.xlsx
+++ b/Dati/Resa estrattiva.xlsx
@@ -1,29 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RSTUDIOAPPLICATIVI\Modunivar\Dati\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AD15A5-4CA1-487B-86BC-9CBD96FF4D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="20115" windowHeight="8520"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resa estrattiva" sheetId="4" r:id="rId1"/>
+    <sheet name="Costruzione" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
   <si>
     <t>Resa</t>
+  </si>
+  <si>
+    <t>Campione#</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -60,27 +70,127 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5BD20C6-666D-4F11-9D91-89AA5DBE1479}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1571625" y="209550"/>
+          <a:ext cx="11163300" cy="714375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="it-IT" sz="1100"/>
+            <a:t>La tabella riporta i dati di resa estrattiva (%p/p) di un principio attivo isolato da 10 prelievi di un lotto di materia prima vegetale fornita ad una azienda farmaceutica.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="it-IT" sz="1100"/>
+            <a:t>Calcolare</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="it-IT" sz="1100" baseline="0"/>
+            <a:t> la media della resa estrattiva e dire se il risultato, riferito a 100 grammi di materia prima è conforme alla specifica del fornitore che dichiara un titolo di attivo pari a 20 mg/100 g.</a:t>
+          </a:r>
+          <a:endParaRPr lang="it-IT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -118,7 +228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -152,6 +262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,9 +297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -361,64 +473,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>13.838709677420338</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>18.766666666666747</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>17.850000000000442</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>23.049999999997794</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>19.266666666666765</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>20.870967741938415</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>17.35483870967823</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>22.370967741935491</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>21.449999999999157</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>19.403225806451658</v>
       </c>
@@ -427,4 +539,106 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{946ED732-B40F-4C79-A740-ACB337C47EE5}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>13.838709677420338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>18.766666666666747</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>17.850000000000442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>23.049999999997794</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>19.266666666666765</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>20.870967741938415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17.35483870967823</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22.370967741935491</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>21.449999999999157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>19.403225806451658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>